--- a/SubRes_Tmpl/SubRES_FossilELC_Trans.xlsx
+++ b/SubRes_Tmpl/SubRES_FossilELC_Trans.xlsx
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="499">
   <si>
     <t>Workbook purpose:</t>
   </si>
@@ -2044,6 +2044,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="1"/>
@@ -2055,20 +2066,9 @@
       <charset val="0"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -38519,8 +38519,7 @@
     <col min="14" max="14" width="28.5454545454545" customWidth="1"/>
     <col min="15" max="15" width="9.09090909090909" customWidth="1"/>
     <col min="16" max="16" width="12.8181818181818"/>
-    <col min="17" max="17" width="9.54545454545454"/>
-    <col min="18" max="18" width="10.5454545454545"/>
+    <col min="17" max="18" width="10.5454545454545"/>
     <col min="20" max="21" width="34.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
@@ -38928,7 +38927,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="14" ht="16" spans="5:8">
+    <row r="14" ht="16" spans="5:66">
       <c r="E14" s="3" t="s">
         <v>493</v>
       </c>
@@ -38943,8 +38942,143 @@
         <f>[1]added_EnergyUse_for_Manu!$AW$26</f>
         <v>0.0478</v>
       </c>
+      <c r="N14" t="s">
+        <v>491</v>
+      </c>
+      <c r="O14" t="s">
+        <v>456</v>
+      </c>
+      <c r="P14" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>149</v>
+      </c>
+      <c r="R14" t="s">
+        <v>296</v>
+      </c>
+      <c r="T14" t="s">
+        <v>491</v>
+      </c>
+      <c r="U14" t="s">
+        <v>456</v>
+      </c>
+      <c r="V14" t="s">
+        <v>10</v>
+      </c>
+      <c r="W14" t="s">
+        <v>149</v>
+      </c>
+      <c r="X14" t="s">
+        <v>296</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>491</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>456</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>296</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>491</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>456</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>149</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>296</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>491</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>456</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>149</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>296</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>491</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>456</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>149</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>296</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>491</v>
+      </c>
+      <c r="AY14" t="s">
+        <v>456</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>10</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>149</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>296</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>491</v>
+      </c>
+      <c r="BE14" t="s">
+        <v>456</v>
+      </c>
+      <c r="BF14" t="s">
+        <v>10</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>149</v>
+      </c>
+      <c r="BH14" t="s">
+        <v>296</v>
+      </c>
+      <c r="BJ14" t="s">
+        <v>491</v>
+      </c>
+      <c r="BK14" t="s">
+        <v>456</v>
+      </c>
+      <c r="BL14" t="s">
+        <v>10</v>
+      </c>
+      <c r="BM14" t="s">
+        <v>149</v>
+      </c>
+      <c r="BN14" t="s">
+        <v>296</v>
+      </c>
     </row>
-    <row r="15" ht="16" spans="5:8">
+    <row r="15" ht="16" spans="5:66">
       <c r="E15" s="3" t="s">
         <v>493</v>
       </c>
@@ -38958,6 +39092,165 @@
       <c r="H15" s="6">
         <f>[1]added_EnergyUse_for_Manu!$AW$27</f>
         <v>0.1895</v>
+      </c>
+      <c r="N15" t="s">
+        <v>465</v>
+      </c>
+      <c r="O15">
+        <v>2023</v>
+      </c>
+      <c r="P15">
+        <f>P5/2</f>
+        <v>40.1915883333333</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" ref="Q15:X15" si="1">Q5/2</f>
+        <v>27.743365</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>53.412525</v>
+      </c>
+      <c r="T15" t="s">
+        <v>465</v>
+      </c>
+      <c r="U15">
+        <v>2025</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="1"/>
+        <v>36.4595122738094</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="1"/>
+        <v>25.167195392857</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="1"/>
+        <v>48.4527905357141</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>465</v>
+      </c>
+      <c r="AA15">
+        <v>2030</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" ref="AB15:AD15" si="2">AB5/2</f>
+        <v>31.5791051190476</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="2"/>
+        <v>21.7983582142857</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="2"/>
+        <v>41.9669839285714</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>465</v>
+      </c>
+      <c r="AG15">
+        <v>2035</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" ref="AH15:AJ15" si="3">AH5/2</f>
+        <v>28.7082773809524</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="3"/>
+        <v>19.8166892857144</v>
+      </c>
+      <c r="AJ15">
+        <f t="shared" si="3"/>
+        <v>38.1518035714287</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>465</v>
+      </c>
+      <c r="AM15">
+        <v>2040</v>
+      </c>
+      <c r="AN15">
+        <f t="shared" ref="AN15:AP15" si="4">AN5/2</f>
+        <v>27.8470290595239</v>
+      </c>
+      <c r="AO15">
+        <f t="shared" si="4"/>
+        <v>19.2221886071429</v>
+      </c>
+      <c r="AP15">
+        <f t="shared" si="4"/>
+        <v>37.0072494642858</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>465</v>
+      </c>
+      <c r="AS15">
+        <v>2045</v>
+      </c>
+      <c r="AT15">
+        <f t="shared" ref="AT15:AV15" si="5">AT5/2</f>
+        <v>26.7331478971429</v>
+      </c>
+      <c r="AU15">
+        <f t="shared" si="5"/>
+        <v>18.4533010628572</v>
+      </c>
+      <c r="AV15">
+        <f t="shared" si="5"/>
+        <v>35.5269594857144</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>465</v>
+      </c>
+      <c r="AY15">
+        <v>2050</v>
+      </c>
+      <c r="AZ15">
+        <f t="shared" ref="AZ15:BB15" si="6">AZ5/2</f>
+        <v>25.6638219812572</v>
+      </c>
+      <c r="BA15">
+        <f t="shared" si="6"/>
+        <v>17.7151690203429</v>
+      </c>
+      <c r="BB15">
+        <f t="shared" si="6"/>
+        <v>34.1058811062858</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>465</v>
+      </c>
+      <c r="BE15">
+        <v>2100</v>
+      </c>
+      <c r="BF15">
+        <f t="shared" ref="BF15:BH15" si="7">BF5/2</f>
+        <v>25.6638219812572</v>
+      </c>
+      <c r="BG15">
+        <f t="shared" si="7"/>
+        <v>17.7151690203429</v>
+      </c>
+      <c r="BH15">
+        <f t="shared" si="7"/>
+        <v>34.1058811062858</v>
+      </c>
+      <c r="BJ15" t="s">
+        <v>465</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>3</v>
+      </c>
+      <c r="BM15">
+        <v>3</v>
+      </c>
+      <c r="BN15">
+        <v>3</v>
       </c>
     </row>
     <row r="16" ht="16" spans="5:8">
